--- a/ozone/multistate/test_ozone_VTZP_MS_3_70_30_energies.xlsx
+++ b/ozone/multistate/test_ozone_VTZP_MS_3_70_30_energies.xlsx
@@ -485,7 +485,7 @@
         <v>-0.5729767853565673</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5754210948944092</v>
+        <v>-0.5711220502853394</v>
       </c>
       <c r="F2" t="n">
         <v>-225.15038093</v>
@@ -494,7 +494,7 @@
         <v>-224.57740433</v>
       </c>
       <c r="H2" t="n">
-        <v>-225.1528254248944</v>
+        <v>-225.1485263802853</v>
       </c>
     </row>
     <row r="3">
@@ -517,7 +517,7 @@
         <v>-0.5733950976508713</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5767775774002075</v>
+        <v>-0.5766736268997192</v>
       </c>
       <c r="F3" t="n">
         <v>-225.14553565</v>
@@ -526,7 +526,7 @@
         <v>-224.57213954</v>
       </c>
       <c r="H3" t="n">
-        <v>-225.1489171174002</v>
+        <v>-225.1488131668997</v>
       </c>
     </row>
     <row r="4">
@@ -549,7 +549,7 @@
         <v>-0.6034229178793995</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6066023111343384</v>
+        <v>-0.6049045324325562</v>
       </c>
       <c r="F4" t="n">
         <v>-225.15110821</v>
@@ -558,7 +558,7 @@
         <v>-224.54768734</v>
       </c>
       <c r="H4" t="n">
-        <v>-225.1542896511343</v>
+        <v>-225.1525918724326</v>
       </c>
     </row>
     <row r="5">
@@ -581,7 +581,7 @@
         <v>-0.5706820623871101</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5707693099975586</v>
+        <v>-0.5702124834060669</v>
       </c>
       <c r="F5" t="n">
         <v>-225.18435946</v>
@@ -590,7 +590,7 @@
         <v>-224.61367603</v>
       </c>
       <c r="H5" t="n">
-        <v>-225.1844453399976</v>
+        <v>-225.1838885134061</v>
       </c>
     </row>
     <row r="6">
@@ -613,7 +613,7 @@
         <v>-0.5725243397689629</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5712261199951172</v>
+        <v>-0.5707176923751831</v>
       </c>
       <c r="F6" t="n">
         <v>-225.15596082</v>
@@ -622,7 +622,7 @@
         <v>-224.58343448</v>
       </c>
       <c r="H6" t="n">
-        <v>-225.1546605999951</v>
+        <v>-225.1541521723752</v>
       </c>
     </row>
     <row r="7">
@@ -645,7 +645,7 @@
         <v>-0.5715870074754034</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5707957744598389</v>
+        <v>-0.5694580674171448</v>
       </c>
       <c r="F7" t="n">
         <v>-225.16910585</v>
@@ -654,7 +654,7 @@
         <v>-224.59751859</v>
       </c>
       <c r="H7" t="n">
-        <v>-225.1683143644598</v>
+        <v>-225.1669766574171</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         <v>-0.5699121168907877</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5735076069831848</v>
+        <v>-0.572704017162323</v>
       </c>
       <c r="F8" t="n">
         <v>-225.20078384</v>
@@ -686,7 +686,7 @@
         <v>-224.63087186</v>
       </c>
       <c r="H8" t="n">
-        <v>-225.2043794669832</v>
+        <v>-225.2035758771623</v>
       </c>
     </row>
     <row r="9">
@@ -709,7 +709,7 @@
         <v>-0.5744787584706563</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5726546049118042</v>
+        <v>-0.5681248307228088</v>
       </c>
       <c r="F9" t="n">
         <v>-225.2235792</v>
@@ -718,7 +718,7 @@
         <v>-224.64910333</v>
       </c>
       <c r="H9" t="n">
-        <v>-225.2217579349118</v>
+        <v>-225.2172281607228</v>
       </c>
     </row>
     <row r="10">
@@ -741,7 +741,7 @@
         <v>-0.5701521808354786</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5654744505882263</v>
+        <v>-0.567560076713562</v>
       </c>
       <c r="F10" t="n">
         <v>-225.20892405</v>
@@ -750,7 +750,7 @@
         <v>-224.63876823</v>
       </c>
       <c r="H10" t="n">
-        <v>-225.2042426805882</v>
+        <v>-225.2063283067136</v>
       </c>
     </row>
     <row r="11">
@@ -773,7 +773,7 @@
         <v>-0.6119886051164722</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6181169748306274</v>
+        <v>-0.6150585412979126</v>
       </c>
       <c r="F11" t="n">
         <v>-225.15481614</v>
@@ -782,7 +782,7 @@
         <v>-224.54282891</v>
       </c>
       <c r="H11" t="n">
-        <v>-225.1609458848306</v>
+        <v>-225.1578874512979</v>
       </c>
     </row>
     <row r="12">
@@ -805,7 +805,7 @@
         <v>-0.5731775317515413</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5717962980270386</v>
+        <v>-0.5733299851417542</v>
       </c>
       <c r="F12" t="n">
         <v>-225.22079726</v>
@@ -814,7 +814,7 @@
         <v>-224.64761912</v>
       </c>
       <c r="H12" t="n">
-        <v>-225.219415418027</v>
+        <v>-225.2209491051418</v>
       </c>
     </row>
     <row r="13">
@@ -837,7 +837,7 @@
         <v>-0.5697242229089197</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5682294964790344</v>
+        <v>-0.5705605745315552</v>
       </c>
       <c r="F13" t="n">
         <v>-225.20558667</v>
@@ -846,7 +846,7 @@
         <v>-224.63586044</v>
       </c>
       <c r="H13" t="n">
-        <v>-225.204089936479</v>
+        <v>-225.2064210145315</v>
       </c>
     </row>
     <row r="14">
@@ -869,7 +869,7 @@
         <v>-0.6086667611073406</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6085395812988281</v>
+        <v>-0.6068127751350403</v>
       </c>
       <c r="F14" t="n">
         <v>-225.1533753</v>
@@ -878,7 +878,7 @@
         <v>-224.54471106</v>
       </c>
       <c r="H14" t="n">
-        <v>-225.1532506412988</v>
+        <v>-225.151523835135</v>
       </c>
     </row>
     <row r="15">
@@ -901,7 +901,7 @@
         <v>-0.5747769951309818</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5752848386764526</v>
+        <v>-0.5795854330062866</v>
       </c>
       <c r="F15" t="n">
         <v>-225.13158491</v>
@@ -910,7 +910,7 @@
         <v>-224.5568066</v>
       </c>
       <c r="H15" t="n">
-        <v>-225.1320914386764</v>
+        <v>-225.1363920330063</v>
       </c>
     </row>
     <row r="16">
@@ -933,7 +933,7 @@
         <v>-0.5707231895471796</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5692167282104492</v>
+        <v>-0.567912220954895</v>
       </c>
       <c r="F16" t="n">
         <v>-225.1836611</v>
@@ -942,7 +942,7 @@
         <v>-224.61294031</v>
       </c>
       <c r="H16" t="n">
-        <v>-225.1821570382104</v>
+        <v>-225.1808525309549</v>
       </c>
     </row>
     <row r="17">
@@ -965,7 +965,7 @@
         <v>-0.5701865895568909</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5703914165496826</v>
+        <v>-0.5685665011405945</v>
       </c>
       <c r="F17" t="n">
         <v>-225.19446127</v>
@@ -974,7 +974,7 @@
         <v>-224.62427669</v>
       </c>
       <c r="H17" t="n">
-        <v>-225.1946681065497</v>
+        <v>-225.1928431911406</v>
       </c>
     </row>
     <row r="18">
@@ -997,7 +997,7 @@
         <v>-0.5698864165646917</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5738450288772583</v>
+        <v>-0.5724183320999146</v>
       </c>
       <c r="F18" t="n">
         <v>-225.20139687</v>
@@ -1006,7 +1006,7 @@
         <v>-224.63150964</v>
       </c>
       <c r="H18" t="n">
-        <v>-225.2053546688772</v>
+        <v>-225.2039279720999</v>
       </c>
     </row>
     <row r="19">
@@ -1029,7 +1029,7 @@
         <v>-0.574007150773048</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5794738531112671</v>
+        <v>-0.5779237747192383</v>
       </c>
       <c r="F19" t="n">
         <v>-225.13900257</v>
@@ -1038,7 +1038,7 @@
         <v>-224.5649943</v>
       </c>
       <c r="H19" t="n">
-        <v>-225.1444681531113</v>
+        <v>-225.1429180747192</v>
       </c>
     </row>
     <row r="20">
@@ -1061,7 +1061,7 @@
         <v>-0.5736998334500785</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.576012134552002</v>
+        <v>-0.5733156204223633</v>
       </c>
       <c r="F20" t="n">
         <v>-225.22209185</v>
@@ -1070,7 +1070,7 @@
         <v>-224.64839101</v>
       </c>
       <c r="H20" t="n">
-        <v>-225.224403144552</v>
+        <v>-225.2217066304224</v>
       </c>
     </row>
     <row r="21">
@@ -1093,7 +1093,7 @@
         <v>-0.5986019961550637</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5958997011184692</v>
+        <v>-0.596794068813324</v>
       </c>
       <c r="F21" t="n">
         <v>-225.14909592</v>
@@ -1102,7 +1102,7 @@
         <v>-224.55049636</v>
       </c>
       <c r="H21" t="n">
-        <v>-225.1463960611185</v>
+        <v>-225.1472904288133</v>
       </c>
     </row>
     <row r="22">
@@ -1125,7 +1125,7 @@
         <v>-0.6073481865312164</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6071754693984985</v>
+        <v>-0.6077167987823486</v>
       </c>
       <c r="F22" t="n">
         <v>-225.15279864</v>
@@ -1134,7 +1134,7 @@
         <v>-224.54544939</v>
       </c>
       <c r="H22" t="n">
-        <v>-225.1526248593985</v>
+        <v>-225.1531661887823</v>
       </c>
     </row>
     <row r="23">
@@ -1157,7 +1157,7 @@
         <v>-0.6080934176856838</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6072824597358704</v>
+        <v>-0.6071944236755371</v>
       </c>
       <c r="F23" t="n">
         <v>-225.15312511</v>
@@ -1166,7 +1166,7 @@
         <v>-224.54503068</v>
       </c>
       <c r="H23" t="n">
-        <v>-225.1523131397359</v>
+        <v>-225.1522251036755</v>
       </c>
     </row>
     <row r="24">
@@ -1189,7 +1189,7 @@
         <v>-0.5712596654392923</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5679950714111328</v>
+        <v>-0.5726888179779053</v>
       </c>
       <c r="F24" t="n">
         <v>-225.17432261</v>
@@ -1198,7 +1198,7 @@
         <v>-224.60306557</v>
       </c>
       <c r="H24" t="n">
-        <v>-225.1710606414111</v>
+        <v>-225.1757543879779</v>
       </c>
     </row>
     <row r="25">
@@ -1221,7 +1221,7 @@
         <v>-0.6011189721848922</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5998640656471252</v>
+        <v>-0.5993741750717163</v>
       </c>
       <c r="F25" t="n">
         <v>-225.15014391</v>
@@ -1230,7 +1230,7 @@
         <v>-224.54902024</v>
       </c>
       <c r="H25" t="n">
-        <v>-225.1488843056471</v>
+        <v>-225.1483944150717</v>
       </c>
     </row>
     <row r="26">
@@ -1253,7 +1253,7 @@
         <v>-0.5725604181121569</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.5722259283065796</v>
+        <v>-0.5740708112716675</v>
       </c>
       <c r="F26" t="n">
         <v>-225.2189662</v>
@@ -1262,7 +1262,7 @@
         <v>-224.64640612</v>
       </c>
       <c r="H26" t="n">
-        <v>-225.2186320483066</v>
+        <v>-225.2204769312717</v>
       </c>
     </row>
     <row r="27">
@@ -1285,7 +1285,7 @@
         <v>-0.5721705153004436</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.5714826583862305</v>
+        <v>-0.5735120177268982</v>
       </c>
       <c r="F27" t="n">
         <v>-225.16067088</v>
@@ -1294,7 +1294,7 @@
         <v>-224.58849966</v>
       </c>
       <c r="H27" t="n">
-        <v>-225.1599823183862</v>
+        <v>-225.1620116777269</v>
       </c>
     </row>
     <row r="28">
@@ -1317,7 +1317,7 @@
         <v>-0.5713825885915944</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.568659782409668</v>
+        <v>-0.5695203542709351</v>
       </c>
       <c r="F28" t="n">
         <v>-225.21460287</v>
@@ -1326,7 +1326,7 @@
         <v>-224.64322174</v>
       </c>
       <c r="H28" t="n">
-        <v>-225.2118815224097</v>
+        <v>-225.2127420942709</v>
       </c>
     </row>
     <row r="29">
@@ -1349,7 +1349,7 @@
         <v>-0.6035984544872954</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6054627299308777</v>
+        <v>-0.6064296960830688</v>
       </c>
       <c r="F29" t="n">
         <v>-225.15118284</v>
@@ -1358,7 +1358,7 @@
         <v>-224.54758585</v>
       </c>
       <c r="H29" t="n">
-        <v>-225.1530485799309</v>
+        <v>-225.1540155460831</v>
       </c>
     </row>
     <row r="30">
@@ -1381,7 +1381,7 @@
         <v>-0.5741322732021592</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5710138082504272</v>
+        <v>-0.5730801820755005</v>
       </c>
       <c r="F30" t="n">
         <v>-225.22298384</v>
@@ -1390,7 +1390,7 @@
         <v>-224.64885131</v>
       </c>
       <c r="H30" t="n">
-        <v>-225.2198651182504</v>
+        <v>-225.2219314920755</v>
       </c>
     </row>
     <row r="31">
@@ -1413,7 +1413,7 @@
         <v>-0.5746010627859426</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5726348161697388</v>
+        <v>-0.5750420689582825</v>
       </c>
       <c r="F31" t="n">
         <v>-225.13323739</v>
@@ -1422,7 +1422,7 @@
         <v>-224.55863816</v>
       </c>
       <c r="H31" t="n">
-        <v>-225.1312729761697</v>
+        <v>-225.1336802289583</v>
       </c>
     </row>
     <row r="32">
@@ -1445,7 +1445,7 @@
         <v>-0.5760680937302514</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5788477659225464</v>
+        <v>-0.5800813436508179</v>
       </c>
       <c r="F32" t="n">
         <v>-225.12083175</v>
@@ -1454,7 +1454,7 @@
         <v>-224.54476329</v>
       </c>
       <c r="H32" t="n">
-        <v>-225.1236110559225</v>
+        <v>-225.1248446336508</v>
       </c>
     </row>
     <row r="33">
@@ -1477,7 +1477,7 @@
         <v>-0.5750754110642475</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5602221488952637</v>
+        <v>-0.5639711618423462</v>
       </c>
       <c r="F33" t="n">
         <v>-225.22437654</v>
@@ -1486,7 +1486,7 @@
         <v>-224.64930261</v>
       </c>
       <c r="H33" t="n">
-        <v>-225.2095247588953</v>
+        <v>-225.2132737718424</v>
       </c>
     </row>
     <row r="34">
@@ -1509,7 +1509,7 @@
         <v>-0.57425583423467</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5770817995071411</v>
+        <v>-0.57603919506073</v>
       </c>
       <c r="F34" t="n">
         <v>-225.13653641</v>
@@ -1518,7 +1518,7 @@
         <v>-224.56228148</v>
       </c>
       <c r="H34" t="n">
-        <v>-225.1393632795071</v>
+        <v>-225.1383206750607</v>
       </c>
     </row>
     <row r="35">
@@ -1541,7 +1541,7 @@
         <v>-0.6018363110695932</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5970402956008911</v>
+        <v>-0.5986678600311279</v>
       </c>
       <c r="F35" t="n">
         <v>-225.15044037</v>
@@ -1550,7 +1550,7 @@
         <v>-224.54860703</v>
       </c>
       <c r="H35" t="n">
-        <v>-225.1456473256009</v>
+        <v>-225.1472748900311</v>
       </c>
     </row>
     <row r="36">
@@ -1573,7 +1573,7 @@
         <v>-0.6048353042071709</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6041311025619507</v>
+        <v>-0.6052494645118713</v>
       </c>
       <c r="F36" t="n">
         <v>-225.15170884</v>
@@ -1582,7 +1582,7 @@
         <v>-224.54687667</v>
       </c>
       <c r="H36" t="n">
-        <v>-225.1510077725619</v>
+        <v>-225.1521261345119</v>
       </c>
     </row>
     <row r="37">
@@ -1605,7 +1605,7 @@
         <v>-0.5726498993786353</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.5721530318260193</v>
+        <v>-0.5728296637535095</v>
       </c>
       <c r="F37" t="n">
         <v>-225.15437523</v>
@@ -1614,7 +1614,7 @@
         <v>-224.58172431</v>
       </c>
       <c r="H37" t="n">
-        <v>-225.153877341826</v>
+        <v>-225.1545539737535</v>
       </c>
     </row>
     <row r="38">
@@ -1637,7 +1637,7 @@
         <v>-0.5727381217231815</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.5740236043930054</v>
+        <v>-0.5742322206497192</v>
       </c>
       <c r="F38" t="n">
         <v>-225.21952541</v>
@@ -1646,7 +1646,7 @@
         <v>-224.64678773</v>
       </c>
       <c r="H38" t="n">
-        <v>-225.220811334393</v>
+        <v>-225.2210199506497</v>
       </c>
     </row>
     <row r="39">
@@ -1669,7 +1669,7 @@
         <v>-0.5722023602066256</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.5734399557113647</v>
+        <v>-0.575602114200592</v>
       </c>
       <c r="F39" t="n">
         <v>-225.21775955</v>
@@ -1678,7 +1678,7 @@
         <v>-224.64555785</v>
       </c>
       <c r="H39" t="n">
-        <v>-225.2189978057114</v>
+        <v>-225.2211599642006</v>
       </c>
     </row>
     <row r="40">
@@ -1701,7 +1701,7 @@
         <v>-0.5987815325972863</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.5942256450653076</v>
+        <v>-0.5980532169342041</v>
       </c>
       <c r="F40" t="n">
         <v>-225.14917195</v>
@@ -1710,7 +1710,7 @@
         <v>-224.55038895</v>
       </c>
       <c r="H40" t="n">
-        <v>-225.1446145950653</v>
+        <v>-225.1484421669342</v>
       </c>
     </row>
     <row r="41">
@@ -1733,7 +1733,7 @@
         <v>-0.5705747913793853</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.5701474547386169</v>
+        <v>-0.5703670978546143</v>
       </c>
       <c r="F41" t="n">
         <v>-225.18643605</v>
@@ -1742,7 +1742,7 @@
         <v>-224.61586148</v>
       </c>
       <c r="H41" t="n">
-        <v>-225.1860089347386</v>
+        <v>-225.1862285778546</v>
       </c>
     </row>
     <row r="42">
@@ -1765,7 +1765,7 @@
         <v>-0.5764001176056167</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.5835831761360168</v>
+        <v>-0.5826482176780701</v>
       </c>
       <c r="F42" t="n">
         <v>-225.11835838</v>
@@ -1774,7 +1774,7 @@
         <v>-224.54195773</v>
       </c>
       <c r="H42" t="n">
-        <v>-225.125540906136</v>
+        <v>-225.1246059476781</v>
       </c>
     </row>
     <row r="43">
@@ -1797,7 +1797,7 @@
         <v>-0.6139654361694777</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.593416690826416</v>
+        <v>-0.6006429195404053</v>
       </c>
       <c r="F43" t="n">
         <v>-225.15562009</v>
@@ -1806,7 +1806,7 @@
         <v>-224.54165841</v>
       </c>
       <c r="H43" t="n">
-        <v>-225.1350751008264</v>
+        <v>-225.1423013295404</v>
       </c>
     </row>
     <row r="44">
@@ -1829,7 +1829,7 @@
         <v>-0.5710106015337281</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.5707606077194214</v>
+        <v>-0.5710344910621643</v>
       </c>
       <c r="F44" t="n">
         <v>-225.2129986</v>
@@ -1838,7 +1838,7 @@
         <v>-224.64198939</v>
       </c>
       <c r="H44" t="n">
-        <v>-225.2127499977194</v>
+        <v>-225.2130238810622</v>
       </c>
     </row>
     <row r="45">
@@ -1861,7 +1861,7 @@
         <v>-0.5746895028958003</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.5741991996765137</v>
+        <v>-0.5769051313400269</v>
       </c>
       <c r="F45" t="n">
         <v>-225.13241137</v>
@@ -1870,7 +1870,7 @@
         <v>-224.5577233</v>
       </c>
       <c r="H45" t="n">
-        <v>-225.1319224996765</v>
+        <v>-225.13462843134</v>
       </c>
     </row>
     <row r="46">
@@ -1893,7 +1893,7 @@
         <v>-0.5748175177900063</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.569395124912262</v>
+        <v>-0.570263147354126</v>
       </c>
       <c r="F46" t="n">
         <v>-225.22407217</v>
@@ -1902,7 +1902,7 @@
         <v>-224.6492542</v>
       </c>
       <c r="H46" t="n">
-        <v>-225.2186493249123</v>
+        <v>-225.2195173473541</v>
       </c>
     </row>
     <row r="47">
@@ -1925,7 +1925,7 @@
         <v>-0.5733237473029531</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.5747093558311462</v>
+        <v>-0.5752878189086914</v>
       </c>
       <c r="F47" t="n">
         <v>-225.14634666</v>
@@ -1934,7 +1934,7 @@
         <v>-224.57302276</v>
       </c>
       <c r="H47" t="n">
-        <v>-225.1477321158311</v>
+        <v>-225.1483105789087</v>
       </c>
     </row>
     <row r="48">
@@ -1957,7 +1957,7 @@
         <v>-0.5758533042024422</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.5805612802505493</v>
+        <v>-0.5828996896743774</v>
       </c>
       <c r="F48" t="n">
         <v>-225.12248361</v>
@@ -1966,7 +1966,7 @@
         <v>-224.54662902</v>
       </c>
       <c r="H48" t="n">
-        <v>-225.1271903002506</v>
+        <v>-225.1295287096744</v>
       </c>
     </row>
     <row r="49">
@@ -1989,7 +1989,7 @@
         <v>-0.5719489427687223</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.5649631023406982</v>
+        <v>-0.5702610015869141</v>
       </c>
       <c r="F49" t="n">
         <v>-225.16377015</v>
@@ -1998,7 +1998,7 @@
         <v>-224.59182099</v>
       </c>
       <c r="H49" t="n">
-        <v>-225.1567840923407</v>
+        <v>-225.1620819915869</v>
       </c>
     </row>
     <row r="50">
@@ -2021,7 +2021,7 @@
         <v>-0.5698628694687208</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.5732986927032471</v>
+        <v>-0.5730265974998474</v>
       </c>
       <c r="F50" t="n">
         <v>-225.20200627</v>
@@ -2030,7 +2030,7 @@
         <v>-224.63214336</v>
       </c>
       <c r="H50" t="n">
-        <v>-225.2054420527032</v>
+        <v>-225.2051699574998</v>
       </c>
     </row>
     <row r="51">
@@ -2053,7 +2053,7 @@
         <v>-0.6104598799429023</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.609467625617981</v>
+        <v>-0.6110690832138062</v>
       </c>
       <c r="F51" t="n">
         <v>-225.15416102</v>
@@ -2062,7 +2062,7 @@
         <v>-224.54370228</v>
       </c>
       <c r="H51" t="n">
-        <v>-225.153169905618</v>
+        <v>-225.1547713632138</v>
       </c>
     </row>
     <row r="52">
@@ -2085,7 +2085,7 @@
         <v>-0.6066184946836062</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.6105352640151978</v>
+        <v>-0.6077966690063477</v>
       </c>
       <c r="F52" t="n">
         <v>-225.15248016</v>
@@ -2094,7 +2094,7 @@
         <v>-224.5458611</v>
       </c>
       <c r="H52" t="n">
-        <v>-225.1563963640152</v>
+        <v>-225.1536577690063</v>
       </c>
     </row>
     <row r="53">
@@ -2117,7 +2117,7 @@
         <v>-0.5752480166933038</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.5772924423217773</v>
+        <v>-0.5787102580070496</v>
       </c>
       <c r="F53" t="n">
         <v>-225.12744774</v>
@@ -2126,7 +2126,7 @@
         <v>-224.55220009</v>
       </c>
       <c r="H53" t="n">
-        <v>-225.1294925323218</v>
+        <v>-225.1309103480071</v>
       </c>
     </row>
     <row r="54">
@@ -2149,7 +2149,7 @@
         <v>-0.5976799657871974</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.6145586967468262</v>
+        <v>-0.6163852214813232</v>
       </c>
       <c r="F54" t="n">
         <v>-225.1487145</v>
@@ -2158,7 +2158,7 @@
         <v>-224.55103545</v>
       </c>
       <c r="H54" t="n">
-        <v>-225.1655941467468</v>
+        <v>-225.1674206714813</v>
       </c>
     </row>
     <row r="55">
@@ -2181,7 +2181,7 @@
         <v>-0.5713000434703812</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.5706925988197327</v>
+        <v>-0.5714747309684753</v>
       </c>
       <c r="F55" t="n">
         <v>-225.17358503</v>
@@ -2190,7 +2190,7 @@
         <v>-224.60228268</v>
       </c>
       <c r="H55" t="n">
-        <v>-225.1729752788197</v>
+        <v>-225.1737574109685</v>
       </c>
     </row>
     <row r="56">
@@ -2213,7 +2213,7 @@
         <v>-0.5724032009911468</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.5730579495429993</v>
+        <v>-0.5736736059188843</v>
       </c>
       <c r="F56" t="n">
         <v>-225.15753907</v>
@@ -2222,7 +2222,7 @@
         <v>-224.58513419</v>
       </c>
       <c r="H56" t="n">
-        <v>-225.158192139543</v>
+        <v>-225.1588077959189</v>
       </c>
     </row>
     <row r="57">
@@ -2245,7 +2245,7 @@
         <v>-0.5984175238173477</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.5952693223953247</v>
+        <v>-0.596741795539856</v>
       </c>
       <c r="F57" t="n">
         <v>-225.14901991</v>
@@ -2254,7 +2254,7 @@
         <v>-224.55060361</v>
       </c>
       <c r="H57" t="n">
-        <v>-225.1458729323953</v>
+        <v>-225.1473454055399</v>
       </c>
     </row>
     <row r="58">
@@ -2277,7 +2277,7 @@
         <v>-0.5722883940892329</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.5702459216117859</v>
+        <v>-0.5723608136177063</v>
       </c>
       <c r="F58" t="n">
         <v>-225.15910909</v>
@@ -2286,7 +2286,7 @@
         <v>-224.58682254</v>
       </c>
       <c r="H58" t="n">
-        <v>-225.1570684616118</v>
+        <v>-225.1591833536177</v>
       </c>
     </row>
     <row r="59">
@@ -2309,7 +2309,7 @@
         <v>-0.6039537019514605</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.6038881540298462</v>
+        <v>-0.6057332754135132</v>
       </c>
       <c r="F59" t="n">
         <v>-225.15133214</v>
@@ -2318,7 +2318,7 @@
         <v>-224.54738287</v>
       </c>
       <c r="H59" t="n">
-        <v>-225.1512710240299</v>
+        <v>-225.1531161454135</v>
       </c>
     </row>
     <row r="60">
@@ -2341,7 +2341,7 @@
         <v>-0.5707284683027058</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.5712668895721436</v>
+        <v>-0.5704913139343262</v>
       </c>
       <c r="F60" t="n">
         <v>-225.21171224</v>
@@ -2350,7 +2350,7 @@
         <v>-224.64098524</v>
       </c>
       <c r="H60" t="n">
-        <v>-225.2122521295721</v>
+        <v>-225.2114765539343</v>
       </c>
     </row>
     <row r="61">
@@ -2373,7 +2373,7 @@
         <v>-0.6157100257686676</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.6085209846496582</v>
+        <v>-0.6168935298919678</v>
       </c>
       <c r="F61" t="n">
         <v>-225.15627484</v>
@@ -2382,7 +2382,7 @@
         <v>-224.54056667</v>
       </c>
       <c r="H61" t="n">
-        <v>-225.1490876546497</v>
+        <v>-225.157460199892</v>
       </c>
     </row>
     <row r="62">
@@ -2405,7 +2405,7 @@
         <v>-0.6126860910489422</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.612057089805603</v>
+        <v>-0.6099587678909302</v>
       </c>
       <c r="F62" t="n">
         <v>-225.15511015</v>
@@ -2414,7 +2414,7 @@
         <v>-224.54241734</v>
       </c>
       <c r="H62" t="n">
-        <v>-225.1544744298056</v>
+        <v>-225.1523761078909</v>
       </c>
     </row>
     <row r="63">
@@ -2437,7 +2437,7 @@
         <v>-0.56983868476376</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.5719161033630371</v>
+        <v>-0.5715987682342529</v>
       </c>
       <c r="F63" t="n">
         <v>-225.2026122</v>
@@ -2446,7 +2446,7 @@
         <v>-224.63277315</v>
       </c>
       <c r="H63" t="n">
-        <v>-225.204689253363</v>
+        <v>-225.2043719182342</v>
       </c>
     </row>
     <row r="64">
@@ -2469,7 +2469,7 @@
         <v>-0.5696854307615137</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.5669537782669067</v>
+        <v>-0.5685861110687256</v>
       </c>
       <c r="F64" t="n">
         <v>-225.20675067</v>
@@ -2478,7 +2478,7 @@
         <v>-224.63706661</v>
       </c>
       <c r="H64" t="n">
-        <v>-225.2040203882669</v>
+        <v>-225.2056527210687</v>
       </c>
     </row>
     <row r="65">
@@ -2501,7 +2501,7 @@
         <v>-0.5705396290001568</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.5713635683059692</v>
+        <v>-0.5699529647827148</v>
       </c>
       <c r="F65" t="n">
         <v>-225.18712249</v>
@@ -2510,7 +2510,7 @@
         <v>-224.61658322</v>
       </c>
       <c r="H65" t="n">
-        <v>-225.187946788306</v>
+        <v>-225.1865361847827</v>
       </c>
     </row>
     <row r="66">
@@ -2533,7 +2533,7 @@
         <v>-0.6021886758040607</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.5980451703071594</v>
+        <v>-0.5987470149993896</v>
       </c>
       <c r="F66" t="n">
         <v>-225.15058854</v>
@@ -2542,7 +2542,7 @@
         <v>-224.54840141</v>
       </c>
       <c r="H66" t="n">
-        <v>-225.1464465803072</v>
+        <v>-225.1471484249994</v>
       </c>
     </row>
     <row r="67">
@@ -2565,7 +2565,7 @@
         <v>-0.5704686464712165</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5710112452507019</v>
+        <v>-0.5690724849700928</v>
       </c>
       <c r="F67" t="n">
         <v>-225.1884852</v>
@@ -2574,7 +2574,7 @@
         <v>-224.61801487</v>
       </c>
       <c r="H67" t="n">
-        <v>-225.1890261152507</v>
+        <v>-225.1870873549701</v>
       </c>
     </row>
     <row r="68">
@@ -2597,7 +2597,7 @@
         <v>-0.6150894474652397</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.6087806224822998</v>
+        <v>-0.612589418888092</v>
       </c>
       <c r="F68" t="n">
         <v>-225.1560492</v>
@@ -2606,7 +2606,7 @@
         <v>-224.54096077</v>
       </c>
       <c r="H68" t="n">
-        <v>-225.1497413924823</v>
+        <v>-225.1535501888881</v>
       </c>
     </row>
     <row r="69">
@@ -2629,7 +2629,7 @@
         <v>-0.6060819905245992</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.6100194454193115</v>
+        <v>-0.6084157228469849</v>
       </c>
       <c r="F69" t="n">
         <v>-225.15224536</v>
@@ -2638,7 +2638,7 @@
         <v>-224.54616741</v>
       </c>
       <c r="H69" t="n">
-        <v>-225.1561868554193</v>
+        <v>-225.154583132847</v>
       </c>
     </row>
     <row r="70">
@@ -2661,7 +2661,7 @@
         <v>-0.6134413273039596</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.6122116446495056</v>
+        <v>-0.6100996732711792</v>
       </c>
       <c r="F70" t="n">
         <v>-225.15541291</v>
@@ -2670,7 +2670,7 @@
         <v>-224.54197483</v>
       </c>
       <c r="H70" t="n">
-        <v>-225.1541864746495</v>
+        <v>-225.1520745032712</v>
       </c>
     </row>
     <row r="71">
@@ -2693,7 +2693,7 @@
         <v>-0.6092492081672025</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.6093729734420776</v>
+        <v>-0.6082122325897217</v>
       </c>
       <c r="F71" t="n">
         <v>-225.1536309</v>
@@ -2702,7 +2702,7 @@
         <v>-224.54438448</v>
       </c>
       <c r="H71" t="n">
-        <v>-225.1537574534421</v>
+        <v>-225.1525967125897</v>
       </c>
     </row>
     <row r="72">
@@ -2725,7 +2725,7 @@
         <v>-0.5709984999126529</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.5695980787277222</v>
+        <v>-0.5720424652099609</v>
       </c>
       <c r="F72" t="n">
         <v>-225.17869154</v>
@@ -2734,7 +2734,7 @@
         <v>-224.607694</v>
       </c>
       <c r="H72" t="n">
-        <v>-225.1772920787277</v>
+        <v>-225.17973646521</v>
       </c>
     </row>
     <row r="73">
@@ -2757,7 +2757,7 @@
         <v>-0.5724647066168691</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.5723344683647156</v>
+        <v>-0.5708369612693787</v>
       </c>
       <c r="F73" t="n">
         <v>-225.15675077</v>
@@ -2766,7 +2766,7 @@
         <v>-224.58428553</v>
       </c>
       <c r="H73" t="n">
-        <v>-225.1566199983647</v>
+        <v>-225.1551224912694</v>
       </c>
     </row>
     <row r="74">
@@ -2789,7 +2789,7 @@
         <v>-0.5730419894785765</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.5754197835922241</v>
+        <v>-0.5716508626937866</v>
       </c>
       <c r="F74" t="n">
         <v>-225.14957731</v>
@@ -2798,7 +2798,7 @@
         <v>-224.57653308</v>
       </c>
       <c r="H74" t="n">
-        <v>-225.1519528635922</v>
+        <v>-225.1481839426938</v>
       </c>
     </row>
     <row r="75">
@@ -2821,7 +2821,7 @@
         <v>-0.57421897592723</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.5727462768554688</v>
+        <v>-0.5745888948440552</v>
       </c>
       <c r="F75" t="n">
         <v>-225.22314238</v>
@@ -2830,7 +2830,7 @@
         <v>-224.6489239</v>
       </c>
       <c r="H75" t="n">
-        <v>-225.2216701768555</v>
+        <v>-225.2235127948441</v>
       </c>
     </row>
     <row r="76">
@@ -2853,7 +2853,7 @@
         <v>-0.5740485705345985</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.5721582174301147</v>
+        <v>-0.5737397074699402</v>
       </c>
       <c r="F76" t="n">
         <v>-225.22281885</v>
@@ -2862,7 +2862,7 @@
         <v>-224.64877247</v>
       </c>
       <c r="H76" t="n">
-        <v>-225.2209306874301</v>
+        <v>-225.22251217747</v>
       </c>
     </row>
     <row r="77">
@@ -2885,7 +2885,7 @@
         <v>-0.5706315571849574</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.5675735473632812</v>
+        <v>-0.5689259767532349</v>
       </c>
       <c r="F77" t="n">
         <v>-225.21126824</v>
@@ -2894,7 +2894,7 @@
         <v>-224.64063538</v>
       </c>
       <c r="H77" t="n">
-        <v>-225.2082089273633</v>
+        <v>-225.2095613567532</v>
       </c>
     </row>
     <row r="78">
@@ -2917,7 +2917,7 @@
         <v>-0.6028930064052287</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.6024084091186523</v>
+        <v>-0.6023932695388794</v>
       </c>
       <c r="F78" t="n">
         <v>-225.15088523</v>
@@ -2926,7 +2926,7 @@
         <v>-224.54799256</v>
       </c>
       <c r="H78" t="n">
-        <v>-225.1504009691187</v>
+        <v>-225.1503858295389</v>
       </c>
     </row>
     <row r="79">
@@ -2949,7 +2949,7 @@
         <v>-0.5743027153048268</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.5737321376800537</v>
+        <v>-0.5750315189361572</v>
       </c>
       <c r="F79" t="n">
         <v>-225.2232944</v>
@@ -2958,7 +2958,7 @@
         <v>-224.64899001</v>
       </c>
       <c r="H79" t="n">
-        <v>-225.2227221476801</v>
+        <v>-225.2240215289362</v>
       </c>
     </row>
     <row r="80">
@@ -2981,7 +2981,7 @@
         <v>-0.5694083190666404</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.5670685768127441</v>
+        <v>-0.5649706125259399</v>
       </c>
       <c r="F80" t="n">
         <v>-225.21550047</v>
@@ -2990,7 +2990,7 @@
         <v>-224.64609355</v>
       </c>
       <c r="H80" t="n">
-        <v>-225.2131621268127</v>
+        <v>-225.2110641625259</v>
       </c>
     </row>
     <row r="81">
@@ -3013,7 +3013,7 @@
         <v>-0.6004073735440025</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.5869206190109253</v>
+        <v>-0.5858014822006226</v>
       </c>
       <c r="F81" t="n">
         <v>-225.14984666</v>
@@ -3022,7 +3022,7 @@
         <v>-224.54943721</v>
       </c>
       <c r="H81" t="n">
-        <v>-225.1363578290109</v>
+        <v>-225.1352386922006</v>
       </c>
     </row>
     <row r="82">
@@ -3045,7 +3045,7 @@
         <v>-0.6057169174033434</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.6029534339904785</v>
+        <v>-0.6004399657249451</v>
       </c>
       <c r="F82" t="n">
         <v>-225.15209065</v>
@@ -3054,7 +3054,7 @@
         <v>-224.54637048</v>
       </c>
       <c r="H82" t="n">
-        <v>-225.1493239139905</v>
+        <v>-225.146810445725</v>
       </c>
     </row>
     <row r="83">
@@ -3077,7 +3077,7 @@
         <v>-0.5708235484094974</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.570578932762146</v>
+        <v>-0.5687556266784668</v>
       </c>
       <c r="F83" t="n">
         <v>-225.21214914</v>
@@ -3086,7 +3086,7 @@
         <v>-224.64132757</v>
       </c>
       <c r="H83" t="n">
-        <v>-225.2119065027621</v>
+        <v>-225.2100831966785</v>
       </c>
     </row>
     <row r="84">
@@ -3109,7 +3109,7 @@
         <v>-0.5693938433051956</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.5684329271316528</v>
+        <v>-0.5638805627822876</v>
       </c>
       <c r="F84" t="n">
         <v>-225.21601304</v>
@@ -3118,7 +3118,7 @@
         <v>-224.64662003</v>
       </c>
       <c r="H84" t="n">
-        <v>-225.2150529571317</v>
+        <v>-225.2105005927823</v>
       </c>
     </row>
     <row r="85">
@@ -3141,7 +3141,7 @@
         <v>-0.5707567292532821</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.5699013471603394</v>
+        <v>-0.5674278736114502</v>
       </c>
       <c r="F85" t="n">
         <v>-225.18295981</v>
@@ -3150,7 +3150,7 @@
         <v>-224.6122011</v>
       </c>
       <c r="H85" t="n">
-        <v>-225.1821024471603</v>
+        <v>-225.1796289736114</v>
       </c>
     </row>
     <row r="86">
@@ -3173,7 +3173,7 @@
         <v>-0.5728261937064738</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.5723289847373962</v>
+        <v>-0.5733488798141479</v>
       </c>
       <c r="F86" t="n">
         <v>-225.21979412</v>
@@ -3182,7 +3182,7 @@
         <v>-224.64696791</v>
       </c>
       <c r="H86" t="n">
-        <v>-225.2192968947374</v>
+        <v>-225.2203167898141</v>
       </c>
     </row>
     <row r="87">
@@ -3205,7 +3205,7 @@
         <v>-0.5708764228913457</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.5696564316749573</v>
+        <v>-0.5669053792953491</v>
       </c>
       <c r="F87" t="n">
         <v>-225.18083875</v>
@@ -3214,7 +3214,7 @@
         <v>-224.60996314</v>
       </c>
       <c r="H87" t="n">
-        <v>-225.1796195716749</v>
+        <v>-225.1768685192953</v>
       </c>
     </row>
     <row r="88">
@@ -3237,7 +3237,7 @@
         <v>-0.5697020162996813</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.5678831338882446</v>
+        <v>-0.5711170434951782</v>
       </c>
       <c r="F88" t="n">
         <v>-225.20617064</v>
@@ -3246,7 +3246,7 @@
         <v>-224.63646572</v>
       </c>
       <c r="H88" t="n">
-        <v>-225.2043488538882</v>
+        <v>-225.2075827634952</v>
       </c>
     </row>
     <row r="89">
@@ -3269,7 +3269,7 @@
         <v>-0.5738506386805673</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.5784119367599487</v>
+        <v>-0.575626015663147</v>
       </c>
       <c r="F89" t="n">
         <v>-225.14064248</v>
@@ -3278,7 +3278,7 @@
         <v>-224.56679315</v>
       </c>
       <c r="H89" t="n">
-        <v>-225.1452050867599</v>
+        <v>-225.1424191656631</v>
       </c>
     </row>
     <row r="90">
@@ -3301,7 +3301,7 @@
         <v>-0.5998714906526699</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.600544810295105</v>
+        <v>-0.6001108884811401</v>
       </c>
       <c r="F90" t="n">
         <v>-225.14962269</v>
@@ -3310,7 +3310,7 @@
         <v>-224.54975205</v>
       </c>
       <c r="H90" t="n">
-        <v>-225.1502968602951</v>
+        <v>-225.1498629384811</v>
       </c>
     </row>
     <row r="91">
@@ -3333,7 +3333,7 @@
         <v>-0.6174663862374243</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.6203604936599731</v>
+        <v>-0.6165882349014282</v>
       </c>
       <c r="F91" t="n">
         <v>-225.15687414</v>
@@ -3342,7 +3342,7 @@
         <v>-224.53940975</v>
       </c>
       <c r="H91" t="n">
-        <v>-225.15977024366</v>
+        <v>-225.1559979849014</v>
       </c>
     </row>
     <row r="92">
@@ -3365,7 +3365,7 @@
         <v>-0.6088576156552427</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.6097699403762817</v>
+        <v>-0.6081336140632629</v>
       </c>
       <c r="F92" t="n">
         <v>-225.1534599</v>
@@ -3374,7 +3374,7 @@
         <v>-224.54460292</v>
       </c>
       <c r="H92" t="n">
-        <v>-225.1543728603763</v>
+        <v>-225.1527365340633</v>
       </c>
     </row>
     <row r="93">
@@ -3397,7 +3397,7 @@
         <v>-0.5728433961297232</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.5751844048500061</v>
+        <v>-0.5714620351791382</v>
       </c>
       <c r="F93" t="n">
         <v>-225.15198392</v>
@@ -3406,7 +3406,7 @@
         <v>-224.57914015</v>
       </c>
       <c r="H93" t="n">
-        <v>-225.15432455485</v>
+        <v>-225.1506021851791</v>
       </c>
     </row>
   </sheetData>
